--- a/Planilhas/orcamento_onasp.xlsx
+++ b/Planilhas/orcamento_onasp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcelo.cortez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DD07F4-F308-44AD-9398-7373AA2CA3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{C4DD07F4-F308-44AD-9398-7373AA2CA3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F11F7E2-B214-4D62-A16A-58F3E6ED2071}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -1137,7 +1137,7 @@
     <col min="7" max="37" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>

--- a/Planilhas/orcamento_onasp.xlsx
+++ b/Planilhas/orcamento_onasp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{C4DD07F4-F308-44AD-9398-7373AA2CA3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F11F7E2-B214-4D62-A16A-58F3E6ED2071}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{C4DD07F4-F308-44AD-9398-7373AA2CA3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3645F305-11DD-470C-892F-2006A6CF4DA4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="135">
   <si>
     <t>ID</t>
   </si>
@@ -415,6 +415,18 @@
   </si>
   <si>
     <t>https://sei.mj.gov.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=40199139</t>
+  </si>
+  <si>
+    <t>1/2026/ONASP-OP</t>
+  </si>
+  <si>
+    <t>https://sei.mj.gov.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=40199139&amp;id_documento=40201817</t>
+  </si>
+  <si>
+    <t>Minuta 35431311</t>
+  </si>
+  <si>
+    <t>https://sei.mj.gov.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=40199139&amp;id_documento=40216436</t>
   </si>
 </sst>
 </file>
@@ -424,7 +436,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -439,6 +451,12 @@
       <sz val="10"/>
       <color rgb="FF0F3A63"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="3">
@@ -493,10 +511,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -513,8 +532,12 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -528,6 +551,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1785,7 +1812,7 @@
     <col min="4" max="27" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1896,12 +1923,24 @@
       <c r="I2" s="5">
         <v>46141</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="5"/>
+      <c r="J2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L2" s="5">
+        <v>46147</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O2" s="5">
+        <v>46147</v>
+      </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="5"/>
@@ -1916,6 +1955,10 @@
       <c r="AA2" s="5"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{45255C03-46EF-460B-838A-64912979EE1D}"/>
+    <hyperlink ref="N2" r:id="rId2" xr:uid="{5D858FFA-10F2-41CC-8736-4F163165152F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>